--- a/fixtures/acfc_shapes/sttm/pair_6_family_d.xlsx
+++ b/fixtures/acfc_shapes/sttm/pair_6_family_d.xlsx
@@ -787,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2265,6 +2265,207 @@
         </is>
       </c>
       <c r="V15" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>DLK</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>syn_dlk</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>stg_um</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>src_sys_c_authorization</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>SRC_FILE_NAME</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>DLK</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>syn_std</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>src_sys_c_authorization</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SRC_FILE_NAME</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>DLK</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>syn_dlk</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>stg_um</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>src_sys_c_authorization</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>REC_CREATION_TIME</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>DLK</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>syn_std</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>src_sys_c_authorization</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>REC_CREATION_TIME</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>DLK</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>syn_dlk</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>stg_um</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>src_sys_c_authorization</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>REC_UPDATED_TIME</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>DLK</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>syn_std</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>src_sys_c_authorization</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>REC_UPDATED_TIME</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
